--- a/Data/FRB_Surajit.xlsx
+++ b/Data/FRB_Surajit.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\Research\FRB\cosmology\FRB_GW_association_cosmo\Notebooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\Research\FRB\cosmology\FRB_cosmology\code\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA96D15-A005-4B39-8F93-8BB249741B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F942B39E-1FA2-4709-98C5-DEF5BB0543ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{5C9607F5-72C0-4E57-83BF-8A0CBC4332AB}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{877481C1-7211-4619-B9A9-6AC551D82B42}"/>
   </bookViews>
   <sheets>
     <sheet name="FRB_Surajit" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>FRB</t>
   </si>
@@ -28,214 +28,208 @@
     <t>DM_obs (pc cm^-3)</t>
   </si>
   <si>
+    <t>DM_MW (pc cm^-3)</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>DM_ext</t>
+  </si>
+  <si>
+    <t>FRB 20121102A</t>
+  </si>
+  <si>
+    <t>FRB 20171020A</t>
+  </si>
+  <si>
+    <t>FRB 20180301A</t>
+  </si>
+  <si>
+    <t>FRB 20180916B</t>
+  </si>
+  <si>
+    <t>FRB 20180924B</t>
+  </si>
+  <si>
+    <t>FRB 20181112A</t>
+  </si>
+  <si>
+    <t>FRB 20181220A</t>
+  </si>
+  <si>
+    <t>FRB 20181223C</t>
+  </si>
+  <si>
+    <t>FRB 20190102C</t>
+  </si>
+  <si>
+    <t>FRB 20190110C</t>
+  </si>
+  <si>
+    <t>FRB 20190303A</t>
+  </si>
+  <si>
+    <t>FRB 20190418A</t>
+  </si>
+  <si>
+    <t>FRB 20190425A</t>
+  </si>
+  <si>
+    <t>FRB 20190520B</t>
+  </si>
+  <si>
+    <t>FRB 20190523A</t>
+  </si>
+  <si>
+    <t>FRB 20190608B</t>
+  </si>
+  <si>
+    <t>FRB 20190611B</t>
+  </si>
+  <si>
+    <t>FRB 20190614D</t>
+  </si>
+  <si>
+    <t>FRB 20190711A</t>
+  </si>
+  <si>
+    <t>FRB 20190714A</t>
+  </si>
+  <si>
+    <t>FRB 20191001A</t>
+  </si>
+  <si>
+    <t>FRB 20191106C</t>
+  </si>
+  <si>
+    <t>FRB 20191228A</t>
+  </si>
+  <si>
+    <t>FRB 20200223B</t>
+  </si>
+  <si>
+    <t>FRB 20200430A</t>
+  </si>
+  <si>
+    <t>FRB 20200906A</t>
+  </si>
+  <si>
+    <t>FRB 20201123A</t>
+  </si>
+  <si>
+    <t>FRB 20201124A</t>
+  </si>
+  <si>
+    <t>FRB 20210117A</t>
+  </si>
+  <si>
+    <t>FRB 20210320C</t>
+  </si>
+  <si>
+    <t>FRB 20210405I</t>
+  </si>
+  <si>
+    <t>FRB 20210410D</t>
+  </si>
+  <si>
+    <t>FRB 20210603A</t>
+  </si>
+  <si>
+    <t>FRB 20210807D</t>
+  </si>
+  <si>
+    <t>FRB 20211127I</t>
+  </si>
+  <si>
+    <t>FRB 20211203C</t>
+  </si>
+  <si>
+    <t>FRB 20211212A</t>
+  </si>
+  <si>
+    <t>FRB 20220105A</t>
+  </si>
+  <si>
+    <t>FRB 20220207C</t>
+  </si>
+  <si>
+    <t>FRB 20220307B</t>
+  </si>
+  <si>
+    <t>FRB 20220310F</t>
+  </si>
+  <si>
+    <t>FRB 20220319D</t>
+  </si>
+  <si>
+    <t>FRB 20220418A</t>
+  </si>
+  <si>
+    <t>FRB 20220501C</t>
+  </si>
+  <si>
+    <t>FRB 20220506D</t>
+  </si>
+  <si>
+    <t>FRB 20220509G</t>
+  </si>
+  <si>
+    <t>FRB 20220610A</t>
+  </si>
+  <si>
+    <t>FRB 20220725A</t>
+  </si>
+  <si>
+    <t>FRB 20220825A</t>
+  </si>
+  <si>
+    <t>FRB 20220912A</t>
+  </si>
+  <si>
+    <t>FRB 20220914A</t>
+  </si>
+  <si>
+    <t>FRB 20220918A</t>
+  </si>
+  <si>
+    <t>FRB 20220920A</t>
+  </si>
+  <si>
+    <t>FRB 20221012A</t>
+  </si>
+  <si>
+    <t>FRB 20221106A</t>
+  </si>
+  <si>
+    <t>FRB 20230526A</t>
+  </si>
+  <si>
+    <t>FRB 20230708A</t>
+  </si>
+  <si>
+    <t>FRB 20230718A</t>
+  </si>
+  <si>
+    <t>FRB 20230902A</t>
+  </si>
+  <si>
+    <t>FRB 20231226A</t>
+  </si>
+  <si>
+    <t>FRB 20240114A</t>
+  </si>
+  <si>
+    <t>FRB 20240201A</t>
+  </si>
+  <si>
+    <t>FRB 20240210A</t>
+  </si>
+  <si>
+    <t>FRB 20240310A</t>
+  </si>
+  <si>
     <t>E_DM_obs</t>
-  </si>
-  <si>
-    <t>DM_MW (pc cm^-3)</t>
-  </si>
-  <si>
-    <t>z</t>
-  </si>
-  <si>
-    <t>FRB 20121102A</t>
-  </si>
-  <si>
-    <t>FRB 20171020A</t>
-  </si>
-  <si>
-    <t>FRB 20180301A</t>
-  </si>
-  <si>
-    <t>FRB 20180916B</t>
-  </si>
-  <si>
-    <t>FRB 20180924B</t>
-  </si>
-  <si>
-    <t>FRB 20181112A</t>
-  </si>
-  <si>
-    <t>FRB 20181220A</t>
-  </si>
-  <si>
-    <t>FRB 20181223C</t>
-  </si>
-  <si>
-    <t>FRB 20190102C</t>
-  </si>
-  <si>
-    <t>FRB 20190110C</t>
-  </si>
-  <si>
-    <t>FRB 20190303A</t>
-  </si>
-  <si>
-    <t>FRB 20190418A</t>
-  </si>
-  <si>
-    <t>FRB 20190425A</t>
-  </si>
-  <si>
-    <t>FRB 20190520B</t>
-  </si>
-  <si>
-    <t>FRB 20190523A</t>
-  </si>
-  <si>
-    <t>FRB 20190608B</t>
-  </si>
-  <si>
-    <t>FRB 20190611B</t>
-  </si>
-  <si>
-    <t>FRB 20190614D</t>
-  </si>
-  <si>
-    <t>FRB 20190711A</t>
-  </si>
-  <si>
-    <t>FRB 20190714A</t>
-  </si>
-  <si>
-    <t>FRB 20191001A</t>
-  </si>
-  <si>
-    <t>FRB 20191106C</t>
-  </si>
-  <si>
-    <t>FRB 20191228A</t>
-  </si>
-  <si>
-    <t>FRB 20200223B</t>
-  </si>
-  <si>
-    <t>FRB 20200430A</t>
-  </si>
-  <si>
-    <t>FRB 20200906A</t>
-  </si>
-  <si>
-    <t>FRB 20201123A</t>
-  </si>
-  <si>
-    <t>FRB 20201124A</t>
-  </si>
-  <si>
-    <t>FRB 20210320C</t>
-  </si>
-  <si>
-    <t>FRB 20210405I</t>
-  </si>
-  <si>
-    <t>FRB 20210410D</t>
-  </si>
-  <si>
-    <t>FRB 20210603A</t>
-  </si>
-  <si>
-    <t>FRB 20210807D</t>
-  </si>
-  <si>
-    <t>FRB 20211127I</t>
-  </si>
-  <si>
-    <t>FRB 20211203C</t>
-  </si>
-  <si>
-    <t>FRB 20211212A</t>
-  </si>
-  <si>
-    <t>FRB 20220105A</t>
-  </si>
-  <si>
-    <t>FRB 20220207C</t>
-  </si>
-  <si>
-    <t>FRB 20220310F</t>
-  </si>
-  <si>
-    <t>FRB 20220319D</t>
-  </si>
-  <si>
-    <t>FRB 20220418A</t>
-  </si>
-  <si>
-    <t>FRB 20220501C</t>
-  </si>
-  <si>
-    <t>FRB 20220506D</t>
-  </si>
-  <si>
-    <t>FRB 20220509G</t>
-  </si>
-  <si>
-    <t>FRB 20220610A</t>
-  </si>
-  <si>
-    <t>FRB 20220725A</t>
-  </si>
-  <si>
-    <t>FRB 20220825A</t>
-  </si>
-  <si>
-    <t>FRB 20220912A</t>
-  </si>
-  <si>
-    <t>FRB 20220914A</t>
-  </si>
-  <si>
-    <t>FRB 20220918A</t>
-  </si>
-  <si>
-    <t>FRB 20220920A</t>
-  </si>
-  <si>
-    <t>FRB 20221012A</t>
-  </si>
-  <si>
-    <t>FRB 20221106A</t>
-  </si>
-  <si>
-    <t>FRB 20230526A</t>
-  </si>
-  <si>
-    <t>FRB 20230708A</t>
-  </si>
-  <si>
-    <t>FRB 20230718A</t>
-  </si>
-  <si>
-    <t>FRB 20230902A</t>
-  </si>
-  <si>
-    <t>FRB 20231226A</t>
-  </si>
-  <si>
-    <t>FRB 20240114A</t>
-  </si>
-  <si>
-    <t>FRB 20240201A</t>
-  </si>
-  <si>
-    <t>FRB 20240210A</t>
-  </si>
-  <si>
-    <t>FRB 20240310A</t>
-  </si>
-  <si>
-    <t>DM_ext</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Kiritti_DM_ext</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>FRB 20220307B</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>FRB 20210117A</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -243,7 +237,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -403,14 +397,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -843,15 +829,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1206,15 +1190,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A6C6722-8B48-4B34-B58C-77350BB8C300}">
-  <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD79C82F-68ED-4F50-8017-D5BDE3F18E6B}">
+  <dimension ref="A1:F65"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.58203125" customWidth="1"/>
-    <col min="2" max="2" width="8.1640625" customWidth="1"/>
+    <col min="1" max="1" width="14.25" customWidth="1"/>
+    <col min="2" max="2" width="9.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1222,22 +1206,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1258,7 +1239,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1279,7 +1260,7 @@
         <v>76.099999999999994</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1300,7 +1281,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1321,7 +1302,7 @@
         <v>149.30000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1342,7 +1323,7 @@
         <v>320.92</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1363,7 +1344,7 @@
         <v>487.27</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1384,7 +1365,7 @@
         <v>83.4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1405,7 +1386,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1426,7 +1407,7 @@
         <v>306.3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1447,7 +1428,7 @@
         <v>184.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1468,7 +1449,7 @@
         <v>193.4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1489,7 +1470,7 @@
         <v>113.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1510,7 +1491,7 @@
         <v>79.199999999999989</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1531,7 +1512,7 @@
         <v>1091.7</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1552,7 +1533,7 @@
         <v>723.8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1573,7 +1554,7 @@
         <v>301.5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1594,7 +1575,7 @@
         <v>263.57</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1615,7 +1596,7 @@
         <v>875.7</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1636,7 +1617,7 @@
         <v>536.70000000000005</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1657,7 +1638,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1678,7 +1659,7 @@
         <v>462.22</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1699,7 +1680,7 @@
         <v>307.2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1720,7 +1701,7 @@
         <v>264.5</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1741,7 +1722,7 @@
         <v>156.20000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1762,7 +1743,7 @@
         <v>353.1</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1783,7 +1764,7 @@
         <v>541.79999999999995</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1804,7 +1785,7 @@
         <v>181.62</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1825,15 +1806,15 @@
         <v>290.32</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="B30">
         <v>730</v>
       </c>
       <c r="C30">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="D30">
         <v>34.4</v>
@@ -1846,9 +1827,9 @@
         <v>695.6</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31">
         <v>384.8</v>
@@ -1867,9 +1848,9 @@
         <v>342.8</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32">
         <v>565.16999999999996</v>
@@ -1888,9 +1869,9 @@
         <v>49.069999999999936</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33">
         <v>578.78</v>
@@ -1909,9 +1890,9 @@
         <v>522.57999999999993</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34">
         <v>500.14699999999999</v>
@@ -1930,9 +1911,9 @@
         <v>460.14699999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35">
         <v>251.9</v>
@@ -1951,9 +1932,9 @@
         <v>130.69999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36">
         <v>234.83</v>
@@ -1972,9 +1953,9 @@
         <v>192.33</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37">
         <v>636.20000000000005</v>
@@ -1993,9 +1974,9 @@
         <v>573.20000000000005</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38">
         <v>206</v>
@@ -2014,9 +1995,9 @@
         <v>178.9</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39">
         <v>583</v>
@@ -2035,9 +2016,9 @@
         <v>561</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40">
         <v>262.38</v>
@@ -2055,13 +2036,10 @@
         <f t="shared" si="0"/>
         <v>183.07999999999998</v>
       </c>
-      <c r="G40" s="3">
-        <v>182.98</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>69</v>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="B41">
         <v>499.27</v>
@@ -2079,11 +2057,10 @@
         <f t="shared" si="0"/>
         <v>363.57</v>
       </c>
-      <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B42">
         <v>462.24</v>
@@ -2101,13 +2078,10 @@
         <f t="shared" si="0"/>
         <v>416.84000000000003</v>
       </c>
-      <c r="G42" s="3">
-        <v>416.71</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B43">
         <v>110.95</v>
@@ -2125,13 +2099,10 @@
         <f t="shared" si="0"/>
         <v>45.7</v>
       </c>
-      <c r="G43" s="3">
-        <v>-22.31</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B44">
         <v>623.25</v>
@@ -2149,13 +2120,10 @@
         <f t="shared" si="0"/>
         <v>585.65</v>
       </c>
-      <c r="G44" s="3">
-        <v>585.84</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B45">
         <v>449.5</v>
@@ -2170,13 +2138,13 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="F45">
-        <f t="shared" si="0"/>
+        <f>B45-D45</f>
         <v>418.5</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B46">
         <v>396.97</v>
@@ -2194,13 +2162,10 @@
         <f t="shared" si="0"/>
         <v>307.87</v>
       </c>
-      <c r="G46" s="3">
-        <v>307.81</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B47">
         <v>269.52999999999997</v>
@@ -2218,13 +2183,10 @@
         <f t="shared" si="0"/>
         <v>214.32999999999998</v>
       </c>
-      <c r="G47" s="3">
-        <v>214.29</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B48">
         <v>1458</v>
@@ -2243,9 +2205,9 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B49">
         <v>290.39999999999998</v>
@@ -2264,9 +2226,9 @@
         <v>259.39999999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B50">
         <v>651.24</v>
@@ -2284,13 +2246,10 @@
         <f t="shared" si="0"/>
         <v>571.54</v>
       </c>
-      <c r="G50" s="3">
-        <v>571.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B51">
         <v>219.46</v>
@@ -2309,9 +2268,9 @@
         <v>94.460000000000008</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B52">
         <v>631.28</v>
@@ -2329,13 +2288,10 @@
         <f t="shared" si="0"/>
         <v>576.07999999999993</v>
       </c>
-      <c r="G52" s="3">
-        <v>575.86</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B53">
         <v>656.8</v>
@@ -2354,9 +2310,9 @@
         <v>615.79999999999995</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B54">
         <v>314.99</v>
@@ -2374,13 +2330,10 @@
         <f t="shared" si="0"/>
         <v>274.69</v>
       </c>
-      <c r="G54" s="3">
-        <v>274.68</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B55">
         <v>441.08</v>
@@ -2398,13 +2351,10 @@
         <f t="shared" si="0"/>
         <v>386.68</v>
       </c>
-      <c r="G55" s="3">
-        <v>387.85</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B56">
         <v>343.8</v>
@@ -2423,9 +2373,9 @@
         <v>308.8</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B57">
         <v>361.4</v>
@@ -2444,9 +2394,9 @@
         <v>311.39999999999998</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B58">
         <v>411.51</v>
@@ -2465,9 +2415,9 @@
         <v>361.51</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B59">
         <v>476.6</v>
@@ -2486,9 +2436,9 @@
         <v>83.600000000000023</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B60">
         <v>440.1</v>
@@ -2507,9 +2457,9 @@
         <v>406.1</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B61">
         <v>329.9</v>
@@ -2528,9 +2478,9 @@
         <v>184.89999999999998</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B62">
         <v>527.70000000000005</v>
@@ -2549,9 +2499,9 @@
         <v>487.70000000000005</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B63">
         <v>374.5</v>
@@ -2570,9 +2520,9 @@
         <v>336.5</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B64">
         <v>283.73</v>
@@ -2591,9 +2541,9 @@
         <v>252.73000000000002</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B65">
         <v>601.79999999999995</v>
